--- a/bills/JXZFSP01/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP01/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1672,12 +1672,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/25 19:36:27</t>
+          <t>09/01 17:52:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22798</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/23 12:09:30</t>
+          <t>07/25 19:36:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>22798</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1726,12 +1726,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>07/23 12:09:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1753,12 +1753,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1780,12 +1780,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1834,12 +1834,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1861,12 +1861,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1942,12 +1942,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1969,12 +1969,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1996,12 +1996,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2050,12 +2050,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2077,12 +2077,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2185,12 +2185,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2212,12 +2212,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2239,12 +2239,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2266,12 +2266,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2320,83 +2320,110 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>8641561</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1039781.92</t>
+          <t>8641561</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1026542</t>
+          <t>1039781.92</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1039795</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>13239.92</t>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-13.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP01/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/01 16:17:54</t>
+          <t>09/03 15:22:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 19:35:03</t>
+          <t>09/01 16:17:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95990</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11033.33</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 14:41:17</t>
+          <t>07/25 19:35:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>95990</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11033.33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/23 09:59:06</t>
+          <t>07/25 14:41:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 14:51:36</t>
+          <t>07/23 09:59:06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5351.19</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 14:50:15</t>
+          <t>07/22 14:51:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>5351.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/21 19:05:10</t>
+          <t>07/22 14:50:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,39 +846,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,39 +888,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,22 +972,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,17 +1518,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1545,166 +1545,181 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/01 17:52:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/25 19:36:27</t>
+          <t>09/01 17:52:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22798</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1726,12 +1741,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/23 12:09:30</t>
+          <t>07/25 19:36:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>22798</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1753,12 +1768,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>07/23 12:09:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1780,12 +1795,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1795,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1807,12 +1822,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1822,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1834,12 +1849,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1861,12 +1876,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1876,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1888,12 +1903,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1915,12 +1930,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1942,12 +1957,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1957,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1969,12 +1984,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1996,12 +2011,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2023,12 +2038,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2050,12 +2065,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2077,12 +2092,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2104,12 +2119,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2131,12 +2146,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2158,12 +2173,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2173,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2185,12 +2200,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2200,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2212,12 +2227,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2239,12 +2254,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2266,12 +2281,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2281,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2293,12 +2308,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2308,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2320,12 +2335,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2347,83 +2362,110 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>8641561</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1039781.92</t>
+          <t>8741561</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1039795</t>
+          <t>1051830.11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1039795</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>-13.08</t>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>12035.11</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP01/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1714,12 +1714,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/01 17:52:01</t>
+          <t>09/03 17:20:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/25 19:36:27</t>
+          <t>09/01 17:52:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22798</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1768,12 +1768,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/23 12:09:30</t>
+          <t>07/25 19:36:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>22798</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>07/23 12:09:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1822,12 +1822,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1849,12 +1849,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1876,12 +1876,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1930,12 +1930,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1957,12 +1957,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2038,12 +2038,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2065,12 +2065,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2146,12 +2146,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2173,12 +2173,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2200,12 +2200,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2254,12 +2254,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2308,12 +2308,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2362,12 +2362,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2389,83 +2389,110 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>8741561</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1051830.11</t>
+          <t>8741561</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1039795</t>
+          <t>1051830.11</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1051843</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>12035.11</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>-12.89</t>
         </is>
       </c>
     </row>
